--- a/regression_deneme/regression_with_nn/yeşildere caddesi_weekly_true_and_predicted_test.xlsx
+++ b/regression_deneme/regression_with_nn/yeşildere caddesi_weekly_true_and_predicted_test.xlsx
@@ -461,7 +461,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>3.385433139026841</v>
+        <v>3.078765585626081</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>16.68513982122286</v>
+        <v>15.77066330578323</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>18.24165552918225</v>
+        <v>20.31927331432371</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>17.56896785502999</v>
+        <v>18.38667381043441</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>16.18122436096774</v>
+        <v>18.77490617315034</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>18.96773649299626</v>
+        <v>14.99385595718095</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>18.34062916059663</v>
+        <v>15.81928962633614</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>14.03981586706773</v>
+        <v>15.96587641988054</v>
       </c>
     </row>
     <row r="10">
@@ -573,7 +573,7 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>13.89863370268099</v>
+        <v>14.15585408358839</v>
       </c>
     </row>
     <row r="11">
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>10.43932286142948</v>
+        <v>15.07224512805279</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +601,7 @@
         <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>17.73263849638742</v>
+        <v>12.52520489978978</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>10.31276834139133</v>
+        <v>12.82201501355413</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +629,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>14.33861035079232</v>
+        <v>12.65987292805524</v>
       </c>
     </row>
     <row r="15">
@@ -643,7 +643,7 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>12.14886014587289</v>
+        <v>14.11211122076019</v>
       </c>
     </row>
     <row r="16">
@@ -657,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>8.673604732478303</v>
+        <v>12.40693790629296</v>
       </c>
     </row>
     <row r="17">
@@ -671,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>11.87098175291327</v>
+        <v>12.69652285759119</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +685,7 @@
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>11.12366703602734</v>
+        <v>10.66067087579789</v>
       </c>
     </row>
     <row r="19">
@@ -699,7 +699,7 @@
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>9.938319769219342</v>
+        <v>8.413948525570914</v>
       </c>
     </row>
     <row r="20">
@@ -713,7 +713,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>7.40742945681186</v>
+        <v>9.829094160676673</v>
       </c>
     </row>
     <row r="21">
@@ -727,7 +727,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>6.717149511461102</v>
+        <v>8.625725654382174</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>10.50428303285504</v>
+        <v>9.510134084306754</v>
       </c>
     </row>
     <row r="23">
@@ -755,7 +755,7 @@
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>9.502059851402453</v>
+        <v>9.387333698895494</v>
       </c>
     </row>
     <row r="24">
@@ -769,7 +769,7 @@
         <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>13.47310985792616</v>
+        <v>13.61577296162331</v>
       </c>
     </row>
     <row r="25">
@@ -783,7 +783,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>13.15813366802764</v>
+        <v>13.43608055402609</v>
       </c>
     </row>
     <row r="26">
@@ -797,7 +797,7 @@
         <v>15</v>
       </c>
       <c r="D26" t="n">
-        <v>12.49310261030271</v>
+        <v>13.48318281249046</v>
       </c>
     </row>
     <row r="27">
@@ -811,7 +811,7 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>16.20949676595016</v>
+        <v>13.83492297691244</v>
       </c>
     </row>
     <row r="28">
@@ -825,7 +825,7 @@
         <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>13.966149396676</v>
+        <v>13.13720002734443</v>
       </c>
     </row>
     <row r="29">
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>11.4033903368651</v>
+        <v>11.53439725471224</v>
       </c>
     </row>
     <row r="30">
@@ -853,7 +853,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>13.47026397029141</v>
+        <v>10.59157326362602</v>
       </c>
     </row>
     <row r="31">
@@ -867,7 +867,7 @@
         <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>13.7816562403782</v>
+        <v>12.525965069506</v>
       </c>
     </row>
     <row r="32">
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>14.75955687461832</v>
+        <v>11.90714985034642</v>
       </c>
     </row>
   </sheetData>
